--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit pas. Il ne faut pas rire de l'apparence. Maman dit : on joue. On ne rit pas des lunettes, des cheveux ou d'un habit. Maya tend une prune à Inès. Elles marchent ensemble. Maya dit : tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
+          <t>Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit pas. Il ne faut pas rire de l'apparence. On joue. On ne rit pas des lunettes, des cheveux ou d'un habit. Maya tend une prune à Inès. Elles marchent ensemble. Tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit pas. Il ne faut pas rire de l'apparence.
+maman|On joue. On ne rit pas des lunettes, des cheveux ou d'un habit.
+narrateur|Maya tend une prune à Inès. Elles marchent ensemble.
+enfant-f|Tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a des lunettes. Que fait Maya ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya n'a pas ri. Elle a joué avec Inès. Pas rire de l'apparence.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman achète du pain. Maya donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 enfant-f|Tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Inès a des lunettes. Que fait Maya ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Maya n'a pas ri. Elle a joué avec Inès. Pas rire de l'apparence.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman achète du pain. Maya donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya ne rit pas des lunettes</t>
+          <t>La prune violette du marché</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino tend une prune à Mila au marché. Ils marchent entre les étals. On ne rit pas de l'apparence.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit pas. Il ne faut pas rire de l'apparence. On joue. On ne rit pas des lunettes, des cheveux ou d'un habit. Maya tend une prune à Inès. Elles marchent ensemble. Tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
+          <t>Les toiles du marché claquent un peu. Une caisse de prunes violettes sent le sucré. Maman tient un filet de coton. Le pain chaud arrive de loin. Tu as senti le pain, Nino ? Il est chaud. Oui. Il est chaud. Le sol est un peu collant sous les semelles. Une balance fait tic. En ce moment, Nino est au marché avec maman. Mila arrive près de la caisse. Mila a des lunettes neuves. Elles brillent un peu au soleil. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. On ne va pas rire de l'apparence. On joue. Nino va vers Mila. Tu veux une prune ? Oui. On en prend deux. Une pour chacun. La prune est lisse et froide. Nino la tend. Mila la prend. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Ils marchent entre les étals. Un sac en papier froisse. Ça sent le fromage, puis le pain. C'est tout doux. C'est sucré. Bravo. Vous marchez ensemble. C'est du bon travail. Le gilet vert reste boutonné. Les lunettes restent sur le nez. Près du stand de pommes, il y a un banc. On s'assoit un moment ? Oui. Le banc est en bois clair. Il est un peu rêche. Ils croquent la prune. Le jus est froid et rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. On peut aller voir les pommes ? Oui. On y va ensemble. Les pommes sont vertes et rouges. Mila en montre une ronde. Celle-là. Elle brille. On la met dans le filet. Le filet s'alourdit un peu. Ils marchent encore, côte à côte. Le marché continue autour d'eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit pas. Il ne faut pas rire de l'apparence.
-maman|On joue. On ne rit pas des lunettes, des cheveux ou d'un habit.
-narrateur|Maya tend une prune à Inès. Elles marchent ensemble.
-enfant-f|Tes lunettes sont là. C'est tout. Pas rire de l'apparence.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les toiles du marché claquent un peu.
+narrateur|Une caisse de prunes violettes sent le sucré.
+narrateur|Maman tient un filet de coton.
+narrateur|Le pain chaud arrive de loin.
+maman|Tu as senti le pain, Nino ?
+enfant-m|Il est chaud.
+maman|Oui. Il est chaud.
+narrateur|Le sol est un peu collant sous les semelles.
+narrateur|Une balance fait tic.
+narrateur|En ce moment, Nino est au marché avec maman.
+narrateur|Mila arrive près de la caisse.
+narrateur|Mila a des lunettes neuves.
+narrateur|Elles brillent un peu au soleil.
+narrateur|Mila a les cheveux lisses.
+narrateur|Elle porte un gilet vert.
+maman|On joue ensemble.
+maman|On ne va pas rire de l'apparence.
+enfant-m|On joue.
+narrateur|Nino va vers Mila.
+enfant-m|Tu veux une prune ?
+copine|Oui.
+maman|On en prend deux. Une pour chacun.
+narrateur|La prune est lisse et froide.
+narrateur|Nino la tend.
+narrateur|Mila la prend.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+maman|L'habit tient chaud.
+maman|On joue.
+narrateur|Ils marchent entre les étals.
+narrateur|Un sac en papier froisse.
+narrateur|Ça sent le fromage, puis le pain.
+enfant-m|C'est tout doux.
+copine|C'est sucré.
+maman|Bravo.
+maman|Vous marchez ensemble.
+maman|C'est du bon travail.
+narrateur|Le gilet vert reste boutonné.
+narrateur|Les lunettes restent sur le nez.
+narrateur|Près du stand de pommes, il y a un banc.
+maman|On s'assoit un moment ?
+enfant-m|Oui.
+narrateur|Le banc est en bois clair.
+narrateur|Il est un peu rêche.
+narrateur|Ils croquent la prune.
+narrateur|Le jus est froid et rouge.
+maman|On ne rit pas des lunettes, des cheveux ou d'un habit.
+maman|On joue.
+enfant-m|On peut aller voir les pommes ?
+maman|Oui. On y va ensemble.
+narrateur|Les pommes sont vertes et rouges.
+narrateur|Mila en montre une ronde.
+copine|Celle-là.
+enfant-m|Elle brille.
+maman|On la met dans le filet.
+narrateur|Le filet s'alourdit un peu.
+narrateur|Ils marchent encore, côte à côte.
+narrateur|Le marché continue autour d'eux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>marche,prune</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès a des lunettes. Que fait Maya ?</t>
+          <t>Mila a des lunettes. Que fait Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès a des lunettes. Que fait Maya ?</t>
+          <t>narrateur|Mila a des lunettes.
+narrateur|Que fait Nino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya n'a pas ri. Elle a joué avec Inès. Pas rire de l'apparence.</t>
+          <t>Nino n'a pas ri. Il a tendu une prune. Il a marché avec Mila. Bravo, Nino. Tu as fait du bon travail. Pas rire de l'apparence. On a joué. Oui. On a joué.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1742,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya n'a pas ri. Elle a joué avec Inès. Pas rire de l'apparence.</t>
+          <t>narrateur|Nino n'a pas ri.
+narrateur|Il a tendu une prune.
+narrateur|Il a marché avec Mila.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+maman|Pas rire de l'apparence.
+enfant-m|On a joué.
+maman|Oui. On a joué.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman achète du pain. Maya donne la main.</t>
+          <t>Maman achète le pain chaud. Le sac sent le four. Tu donnes la main, Nino ? Oui, maman. Mila agite la main. Merci pour la prune. À demain. Les toiles claquent encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1917,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman achète du pain. Maya donne la main.</t>
+          <t>narrateur|Maman achète le pain chaud.
+narrateur|Le sac sent le four.
+maman|Tu donnes la main, Nino ?
+enfant-m|Oui, maman.
+narrateur|Mila agite la main.
+copine|Merci pour la prune.
+enfant-m|À demain.
+narrateur|Les toiles claquent encore un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a partagé une prune. Bravo. Vous avez marché ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2092,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a partagé une prune.
+maman|Bravo.
+maman|Vous avez marché ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les toiles du marché claquent un peu. Une caisse de prunes violettes sent le sucré. Maman tient un filet de coton. Le pain chaud arrive de loin. Tu as senti le pain, Nino ? Il est chaud. Oui. Il est chaud. Le sol est un peu collant sous les semelles. Une balance fait tic. En ce moment, Nino est au marché avec maman. Mila arrive près de la caisse. Mila a des lunettes neuves. Elles brillent un peu au soleil. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. On ne va pas rire de l'apparence. On joue. Nino va vers Mila. Tu veux une prune ? Oui. On en prend deux. Une pour chacun. La prune est lisse et froide. Nino la tend. Mila la prend. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Ils marchent entre les étals. Un sac en papier froisse. Ça sent le fromage, puis le pain. C'est tout doux. C'est sucré. Bravo. Vous marchez ensemble. C'est du bon travail. Le gilet vert reste boutonné. Les lunettes restent sur le nez. Près du stand de pommes, il y a un banc. On s'assoit un moment ? Oui. Le banc est en bois clair. Il est un peu rêche. Ils croquent la prune. Le jus est froid et rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. On peut aller voir les pommes ? Oui. On y va ensemble. Les pommes sont vertes et rouges. Mila en montre une ronde. Celle-là. Elle brille. On la met dans le filet. Le filet s'alourdit un peu. Ils marchent encore, côte à côte. Le marché continue autour d'eux.</t>
+          <t>Les toiles du marché claquent un peu. Une caisse de prunes violettes sent le sucré. Maman tient un filet de coton. Le pain chaud arrive de loin. Tu as senti le pain, Nino ? Il est chaud. Oui. Il est chaud. Le sol est un peu collant sous les semelles. Une balance fait tic. En ce moment, Nino est au marché avec maman. Mila arrive près de la caisse. Mila a des lunettes neuves. Elles brillent un peu au soleil. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. On ne va pas rire de l'apparence. On joue. Nino va vers Mila. Tu veux une prune ? Oui. On en prend deux. Une pour chacun. La prune est lisse et froide. Nino la tend. Mila la prend. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Ils marchent entre les étals. Un sac en papier froisse. Ça sent le fromage, puis le pain. C'est tout doux. C'est sucré. Bravo. Vous marchez ensemble. C'est du bon travail. Le gilet vert reste boutonné. Les lunettes restent sur le nez. Près du stand de pommes, il y a un banc. On s'assoit un moment ? Oui. Le banc est en bois clair. Il est un peu rêche. Ils croquent la prune. Le jus est froid et rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. On peut aller voir les pommes ? Oui. On y va ensemble. Les pommes sont vertes et rouges. Mila en montre une ronde. Celle-là. Elle brille. On la met dans le filet. Le filet s'alourdit un peu. Il est lourd, le filet ? Un peu. On le porte à deux. Viens. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. Tu as bien senti. C'est vert. Oui. Vert et frais. Une cuillère en bois est sur la table. Elle est lisse et claire. Elle est grande. On la regarde. On ne la prend pas. On reste ensemble. Ils avancent vers les œufs. Les boîtes sont beiges. Ça sent la paille. On a le pain. On a la prune. On a la pomme. C'est bien. On joue. On marche. On marche. Ils marchent encore, côte à côte. Le marché continue autour d'eux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1330,7 +1330,8 @@
 narrateur|Le pain chaud arrive de loin.
 maman|Tu as senti le pain, Nino ?
 enfant-m|Il est chaud.
-maman|Oui. Il est chaud.
+maman|Oui.
+maman|Il est chaud.
 narrateur|Le sol est un peu collant sous les semelles.
 narrateur|Une balance fait tic.
 narrateur|En ce moment, Nino est au marché avec maman.
@@ -1345,7 +1346,8 @@
 narrateur|Nino va vers Mila.
 enfant-m|Tu veux une prune ?
 copine|Oui.
-maman|On en prend deux. Une pour chacun.
+maman|On en prend deux.
+maman|Une pour chacun.
 narrateur|La prune est lisse et froide.
 narrateur|Nino la tend.
 narrateur|Mila la prend.
@@ -1373,13 +1375,44 @@
 maman|On ne rit pas des lunettes, des cheveux ou d'un habit.
 maman|On joue.
 enfant-m|On peut aller voir les pommes ?
-maman|Oui. On y va ensemble.
+maman|Oui.
+maman|On y va ensemble.
 narrateur|Les pommes sont vertes et rouges.
 narrateur|Mila en montre une ronde.
 copine|Celle-là.
 enfant-m|Elle brille.
 maman|On la met dans le filet.
 narrateur|Le filet s'alourdit un peu.
+maman|Il est lourd, le filet ?
+enfant-m|Un peu.
+maman|On le porte à deux.
+maman|Viens.
+narrateur|Nino tient une anse.
+narrateur|Maman tient l'autre.
+narrateur|Mila marche tout près.
+narrateur|Un stand de menthe sent fort.
+enfant-m|Ça pique le nez.
+maman|C'est la menthe.
+maman|Tu as bien senti.
+copine|C'est vert.
+maman|Oui.
+maman|Vert et frais.
+narrateur|Une cuillère en bois est sur la table.
+narrateur|Elle est lisse et claire.
+enfant-m|Elle est grande.
+maman|On la regarde.
+maman|On ne la prend pas.
+maman|On reste ensemble.
+narrateur|Ils avancent vers les œufs.
+narrateur|Les boîtes sont beiges.
+narrateur|Ça sent la paille.
+maman|On a le pain.
+maman|On a la prune.
+maman|On a la pomme.
+maman|C'est bien.
+maman|On joue.
+maman|On marche.
+enfant-m|On marche.
 narrateur|Ils marchent encore, côte à côte.
 narrateur|Le marché continue autour d'eux.</t>
         </is>
@@ -1598,7 +1631,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il a tendu une prune. Il a marché avec Mila. Bravo, Nino. Tu as fait du bon travail. Pas rire de l'apparence. On a joué. Oui. On a joué.</t>
+          <t>Nino n'a pas ri. Il a tendu une prune. Il a marché avec Mila. Bravo, Nino. Tu as fait du bon travail. Pas rire de l'apparence. On a joué. Oui. On a joué. Tu as tendu la prune. Bravo. Le filet repose contre la jambe de maman. Tu as fini de marcher un moment ? On rentre bientôt. Bientôt. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1749,7 +1782,15 @@
 maman|Tu as fait du bon travail.
 maman|Pas rire de l'apparence.
 enfant-m|On a joué.
-maman|Oui. On a joué.</t>
+maman|Oui.
+maman|On a joué.
+maman|Tu as tendu la prune.
+maman|Bravo.
+narrateur|Le filet repose contre la jambe de maman.
+maman|Tu as fini de marcher un moment ?
+enfant-m|On rentre bientôt.
+maman|Bientôt.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -2117,7 +2158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2201,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La prune violette du marché</t>
+          <t>La prune de la tarte</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino tend une prune à Mila au marché. Ils marchent entre les étals. On ne rit pas de l'apparence.</t>
+          <t>Nino veut une prune bien ronde pour la tarte de maman. Il prend une molle. Mila, avec ses lunettes, voit une prune ferme au fond. Ils la portent dans le filet.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les toiles du marché claquent un peu. Une caisse de prunes violettes sent le sucré. Maman tient un filet de coton. Le pain chaud arrive de loin. Tu as senti le pain, Nino ? Il est chaud. Oui. Il est chaud. Le sol est un peu collant sous les semelles. Une balance fait tic. En ce moment, Nino est au marché avec maman. Mila arrive près de la caisse. Mila a des lunettes neuves. Elles brillent un peu au soleil. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. On ne va pas rire de l'apparence. On joue. Nino va vers Mila. Tu veux une prune ? Oui. On en prend deux. Une pour chacun. La prune est lisse et froide. Nino la tend. Mila la prend. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Ils marchent entre les étals. Un sac en papier froisse. Ça sent le fromage, puis le pain. C'est tout doux. C'est sucré. Bravo. Vous marchez ensemble. C'est du bon travail. Le gilet vert reste boutonné. Les lunettes restent sur le nez. Près du stand de pommes, il y a un banc. On s'assoit un moment ? Oui. Le banc est en bois clair. Il est un peu rêche. Ils croquent la prune. Le jus est froid et rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. On peut aller voir les pommes ? Oui. On y va ensemble. Les pommes sont vertes et rouges. Mila en montre une ronde. Celle-là. Elle brille. On la met dans le filet. Le filet s'alourdit un peu. Il est lourd, le filet ? Un peu. On le porte à deux. Viens. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. Tu as bien senti. C'est vert. Oui. Vert et frais. Une cuillère en bois est sur la table. Elle est lisse et claire. Elle est grande. On la regarde. On ne la prend pas. On reste ensemble. Ils avancent vers les œufs. Les boîtes sont beiges. Ça sent la paille. On a le pain. On a la prune. On a la pomme. C'est bien. On joue. On marche. On marche. Ils marchent encore, côte à côte. Le marché continue autour d'eux.</t>
+          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Ses lunettes aident à voir. Au fond. Celle-là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire de l'apparence. Maman dit : on joue. On ne rit pas des lunettes, des cheveux ou d'un habit. Maya tend une prune à Inès. Elles marchent ensemble. Maya dit : tes lunettes sont là. C'est tout. Pas rire de l'apparence.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Ses lunettes aident à voir. Au fond. Celle-là.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,97 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les toiles du marché claquent un peu.
-narrateur|Une caisse de prunes violettes sent le sucré.
+          <t>narrateur|Le four du boulanger souffle une odeur de mie.
+narrateur|Un peu de farine blanchit la planche.
+narrateur|Le pain chaud croustille dans le sac.
+narrateur|Une miette tombe près de la caisse.
 narrateur|Maman tient un filet de coton.
-narrateur|Le pain chaud arrive de loin.
+narrateur|Le filet sent encore la lessive.
+narrateur|Le sol est un peu collant.
 maman|Tu as senti le pain, Nino ?
 enfant-m|Il est chaud.
 maman|Oui.
-maman|Il est chaud.
-narrateur|Le sol est un peu collant sous les semelles.
-narrateur|Une balance fait tic.
-narrateur|En ce moment, Nino est au marché avec maman.
+maman|Il ira avec la tarte.
+narrateur|Nino touche le sac de pain.
+narrateur|Le papier est tiède.
+narrateur|En ce moment, Nino regarde les prunes.
+narrateur|Elles sont violettes et lisses.
+narrateur|Une caisse sent le sucré.
+enfant-m|J'en veux une ronde.
+enfant-m|Pour la tarte.
+maman|On en cherche une ferme.
+maman|Pas trop molle.
 narrateur|Mila arrive près de la caisse.
+narrateur|Ses chaussures collent un peu au sol.
 narrateur|Mila a des lunettes neuves.
-narrateur|Elles brillent un peu au soleil.
 narrateur|Mila a les cheveux lisses.
 narrateur|Elle porte un gilet vert.
 maman|On joue ensemble.
-maman|On ne va pas rire de l'apparence.
-enfant-m|On joue.
-narrateur|Nino va vers Mila.
-enfant-m|Tu veux une prune ?
+enfant-m|Tu m'aides, Mila ?
 copine|Oui.
-maman|On en prend deux.
-maman|Une pour chacun.
-narrateur|La prune est lisse et froide.
-narrateur|Nino la tend.
-narrateur|Mila la prend.
-maman|Les lunettes aident à voir.
-maman|Les cheveux sont les cheveux.
-maman|L'habit tient chaud.
-maman|On joue.
-narrateur|Ils marchent entre les étals.
-narrateur|Un sac en papier froisse.
-narrateur|Ça sent le fromage, puis le pain.
-enfant-m|C'est tout doux.
-copine|C'est sucré.
-maman|Bravo.
-maman|Vous marchez ensemble.
-maman|C'est du bon travail.
-narrateur|Le gilet vert reste boutonné.
-narrateur|Les lunettes restent sur le nez.
-narrateur|Près du stand de pommes, il y a un banc.
-maman|On s'assoit un moment ?
-enfant-m|Oui.
-narrateur|Le banc est en bois clair.
-narrateur|Il est un peu rêche.
-narrateur|Ils croquent la prune.
-narrateur|Le jus est froid et rouge.
-maman|On ne rit pas des lunettes, des cheveux ou d'un habit.
-maman|On joue.
-enfant-m|On peut aller voir les pommes ?
-maman|Oui.
-maman|On y va ensemble.
-narrateur|Les pommes sont vertes et rouges.
-narrateur|Mila en montre une ronde.
-copine|Celle-là.
-enfant-m|Elle brille.
-maman|On la met dans le filet.
-narrateur|Le filet s'alourdit un peu.
-maman|Il est lourd, le filet ?
-enfant-m|Un peu.
-maman|On le porte à deux.
-maman|Viens.
-narrateur|Nino tient une anse.
-narrateur|Maman tient l'autre.
-narrateur|Mila marche tout près.
-narrateur|Un stand de menthe sent fort.
-enfant-m|Ça pique le nez.
-maman|C'est la menthe.
-maman|Tu as bien senti.
-copine|C'est vert.
-maman|Oui.
-maman|Vert et frais.
-narrateur|Une cuillère en bois est sur la table.
-narrateur|Elle est lisse et claire.
-enfant-m|Elle est grande.
-maman|On la regarde.
-maman|On ne la prend pas.
-maman|On reste ensemble.
-narrateur|Ils avancent vers les œufs.
-narrateur|Les boîtes sont beiges.
-narrateur|Ça sent la paille.
-maman|On a le pain.
-maman|On a la prune.
-maman|On a la pomme.
-maman|C'est bien.
-maman|On joue.
-maman|On marche.
-enfant-m|On marche.
-narrateur|Ils marchent encore, côte à côte.
-narrateur|Le marché continue autour d'eux.</t>
+narrateur|Nino prend une prune.
+narrateur|Elle cède un peu sous le doigt.
+enfant-m|Elle est molle.
+maman|On la repose.
+maman|Tout doux, dans la caisse.
+narrateur|Mila se penche sur la caisse.
+narrateur|Ses lunettes aident à voir.
+copine|Au fond.
+copine|Celle-là.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1451,7 +1397,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès a des lunettes. Que fait Maya ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a des lunettes. Que fait Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1461,12 +1407,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>pas rire</t>
+          <t>jouer</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | jouer | ensemble</t>
+          <t>jouer | ensemble | aider | prune | on joue | pas rire</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1481,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On ne rit pas de l'apparence. Que fait Maya ?</t>
+          <t>Nino écoute Mila. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1530,7 +1476,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1606,7 +1552,6 @@
 narrateur|Que fait Nino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1631,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il a tendu une prune. Il a marché avec Mila. Bravo, Nino. Tu as fait du bon travail. Pas rire de l'apparence. On a joué. Oui. On a joué. Tu as tendu la prune. Bravo. Le filet repose contre la jambe de maman. Tu as fini de marcher un moment ? On rentre bientôt. Bientôt. Oui.</t>
+          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Les lunettes aident à voir. On joue. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Elle a joué avec Inès. Pas rire de l'apparence.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Les lunettes aident à voir. On joue. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1699,7 +1644,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1775,25 +1720,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino n'a pas ri.
-narrateur|Il a tendu une prune.
-narrateur|Il a marché avec Mila.
-maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-maman|Pas rire de l'apparence.
-enfant-m|On a joué.
+          <t>narrateur|Nino écoute Mila.
+narrateur|Il prend la prune du fond.
+narrateur|Elle est lisse et ferme.
+maman|Merci, Nino.
+maman|Merci, Mila.
+enfant-m|Elle est ronde.
+copine|Pour la tarte.
+maman|On la met dans le filet.
+narrateur|Le filet s'alourdit un peu.
+narrateur|Le coton se tend.
+maman|Les lunettes aident à voir.
+maman|On joue.
+enfant-m|On prend une pomme aussi ?
 maman|Oui.
-maman|On a joué.
-maman|Tu as tendu la prune.
-maman|Bravo.
-narrateur|Le filet repose contre la jambe de maman.
-maman|Tu as fini de marcher un moment ?
-enfant-m|On rentre bientôt.
-maman|Bientôt.
-maman|Oui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Une pomme rouge.
+narrateur|Mila montre une pomme brillante.
+narrateur|Nino la pose dans le filet.
+enfant-m|Elle est lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1818,12 +1764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman achète le pain chaud. Le sac sent le four. Tu donnes la main, Nino ? Oui, maman. Mila agite la main. Merci pour la prune. À demain. Les toiles claquent encore un peu.</t>
+          <t>La pomme rejoint la prune. Le filet balance. Il est lourd, le filet ? Un peu. On le porte à deux. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. C'est vert. Vert et frais. Ils passent près des œufs. Les boîtes sont beiges. Bravo. Tu as choisi la prune ferme. Le pain chaud tape le bras. Ce soir, la tarte. Oui. Avec ta prune ronde. Et la pomme. Une balance fait tic près d'eux. Les toiles claquent un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman achète du pain. Maya donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pomme rejoint la prune. Le filet balance. Il est lourd, le filet ? Un peu. On le porte à deux. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. C'est vert. Vert et frais. Ils passent près des œufs. Les boîtes sont beiges. Bravo. Tu as choisi la prune ferme. Le pain chaud tape le bras. Ce soir, la tarte. Oui. Avec ta prune ronde. Et la pomme. Une balance fait tic près d'eux. Les toiles claquent un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1886,7 +1832,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1958,17 +1904,32 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman achète le pain chaud.
-narrateur|Le sac sent le four.
-maman|Tu donnes la main, Nino ?
-enfant-m|Oui, maman.
-narrateur|Mila agite la main.
-copine|Merci pour la prune.
-enfant-m|À demain.
-narrateur|Les toiles claquent encore un peu.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La pomme rejoint la prune.
+narrateur|Le filet balance.
+maman|Il est lourd, le filet ?
+enfant-m|Un peu.
+maman|On le porte à deux.
+narrateur|Nino tient une anse.
+narrateur|Maman tient l'autre.
+narrateur|Mila marche tout près.
+narrateur|Un stand de menthe sent fort.
+enfant-m|Ça pique le nez.
+maman|C'est la menthe.
+copine|C'est vert.
+maman|Vert et frais.
+narrateur|Ils passent près des œufs.
+narrateur|Les boîtes sont beiges.
+maman|Bravo.
+maman|Tu as choisi la prune ferme.
+narrateur|Le pain chaud tape le bras.
+enfant-m|Ce soir, la tarte.
+maman|Oui.
+maman|Avec ta prune ronde.
+copine|Et la pomme.
+narrateur|Une balance fait tic près d'eux.
+narrateur|Les toiles claquent un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1993,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a partagé une prune. Bravo. Vous avez marché ensemble. L'histoire est finie.</t>
+          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2054,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2133,13 +2094,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a partagé une prune.
-maman|Bravo.
-maman|Vous avez marché ensemble.
+          <t>narrateur|Le filet tient la prune et la pomme.
+narrateur|Le sac de pain sent le four.
+enfant-m|On a la prune de la tarte.
+maman|Oui.
+maman|Vous avez cherché ensemble.
+narrateur|La farine reste sur la planche.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2158,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2187,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Ses lunettes aident à voir. Au fond. Celle-là.</t>
+          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. Mila, tu cherches avec Nino. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Elle regarde au fond. Au fond. Celle-là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. On joue ensemble. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Ses lunettes aident à voir. Au fond. Celle-là.</t>
+          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. Mila, tu cherches avec Nino. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Elle regarde au fond. Au fond. Celle-là.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
 narrateur|Mila a des lunettes neuves.
 narrateur|Mila a les cheveux lisses.
 narrateur|Elle porte un gilet vert.
-maman|On joue ensemble.
+maman|Mila, tu cherches avec Nino.
 enfant-m|Tu m'aides, Mila ?
 copine|Oui.
 narrateur|Nino prend une prune.
@@ -1358,7 +1358,7 @@
 maman|On la repose.
 maman|Tout doux, dans la caisse.
 narrateur|Mila se penche sur la caisse.
-narrateur|Ses lunettes aident à voir.
+narrateur|Elle regarde au fond.
 copine|Au fond.
 copine|Celle-là.</t>
         </is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Les lunettes aident à voir. On joue. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
+          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Mila a vu au fond. On a la prune. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Les lunettes aident à voir. On joue. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
+          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Mila a vu au fond. On a la prune. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1730,8 +1730,8 @@
 maman|On la met dans le filet.
 narrateur|Le filet s'alourdit un peu.
 narrateur|Le coton se tend.
-maman|Les lunettes aident à voir.
-maman|On joue.
+maman|Mila a vu au fond.
+maman|On a la prune.
 enfant-m|On prend une pomme aussi ?
 maman|Oui.
 maman|Une pomme rouge.
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2192,6 +2192,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche. L'histoire est finie.</t>
+          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche. L'histoire est finie.</t>
+          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,8 +2099,7 @@
 enfant-m|On a la prune de la tarte.
 maman|Oui.
 maman|Vous avez cherché ensemble.
-narrateur|La farine reste sur la planche.
-narrateur|L'histoire est finie.</t>
+narrateur|La farine reste sur la planche.</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2198,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>boulangerie puis marché</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, Inès, maman</t>
+          <t>Nino, Mila, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-03.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La prune de la tarte</t>
+          <t>La prune violette du marché</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boulangerie puis marché</t>
+          <t>marché : toiles, caisse de prunes, filet de coton, pain, balance, banc, pommes, menthe, œufs</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nino, Mila, maman</t>
+          <t>Nino, Mila, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino veut une prune bien ronde pour la tarte de maman. Il prend une molle. Mila, avec ses lunettes, voit une prune ferme au fond. Ils la portent dans le filet.</t>
+          <t>Une toile claque. Sur la caisse, un éclat de cageot brille. Nino veut une prune violette, maintenant, avec Mila. Il saisit trop vite : la prune tombe, le filet se coince. Sourire parti. Mila arrive, lunettes neuves. Un rire commence. Il ferme la bouche, tend une prune. Merci vécu. Il lève trop haut : le jus tache, les lunettes bougent. Il refuse de foncer. L'éclat de cageot tient. La prune est partagée.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. Mila, tu cherches avec Nino. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Elle regarde au fond. Au fond. Celle-là.</t>
+          <t>Une toile claque au-dessus des prunes. J'entends la toile, maman ! Tu l'entends, au-dessus ? Oui, elle claque. Ça sent le sucré, un peu chaud. Tu le sens, Nino ? Oui, papa. Un cageot de bois est ouvert. Des prunes violettes y brillent. Sur la caisse, un éclat de cageot brille. Il brille, papa ! Tu le vois, sur le bois ? Oui, un petit point. Le filet de coton est prêt. Il gratte un peu. On le remplit, Nino ? Oui, avec une prune. Le pain chaud tape le bras de Nino. Il est tiède. Le papier croustille ? Oui, papa. À côté, des pommes rouges attendent. Elles sont lisses, maman. On verra les pommes après ? Après la prune. Une balance fait tic, tout près. J'entends le tic. C'est la balance ? Oui. En ce moment, Nino veut une prune. Je veux une prune, maintenant ! Une prune violette, maman. Avec Mila, Nino ? Oui, maman. Nino saisit trop vite une prune. La prune glisse entre ses doigts. Elle tombe dans le cageot. Elle est tombée ! Nino tire le filet trop vite. Le filet se coince au bord. Il est coincé ! Le coton, Nino ? Il tient au bois. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu, lourdes. Maman s'accroupit à la même hauteur. Tu veux la prune avec Mila ? Oui, maman. Tes mains sont collantes, Nino ? Un peu, papa. Mila arrive près du cageot. Mila ! Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Tu vois Mila, Nino ? Oui, papa. Elles brillent un peu. Elle porte un gilet vert. Tu viens, Mila ? Oui. Nino ouvre la bouche. Un petit rire commence. Oh. Nino ferme la bouche. Il regarde la caisse. Il tend une prune. Pour toi. Mila ne dit rien, d'abord. Elle compte les prunes des yeux. Celle-là. L'éclat de cageot tremble, puis tient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le four du boulanger souffle une odeur de mie. Un peu de farine blanchit la planche. Le pain chaud croustille dans le sac. Une miette tombe près de la caisse. Maman tient un filet de coton. Le filet sent encore la lessive. Le sol est un peu collant. Tu as senti le pain, Nino ? Il est chaud. Oui. Il ira avec la tarte. Nino touche le sac de pain. Le papier est tiède. En ce moment, Nino regarde les prunes. Elles sont violettes et lisses. Une caisse sent le sucré. J'en veux une ronde. Pour la tarte. On en cherche une ferme. Pas trop molle. Mila arrive près de la caisse. Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Mila a les cheveux lisses. Elle porte un gilet vert. Mila, tu cherches avec Nino. Tu m'aides, Mila ? Oui. Nino prend une prune. Elle cède un peu sous le doigt. Elle est molle. On la repose. Tout doux, dans la caisse. Mila se penche sur la caisse. Elle regarde au fond. Au fond. Celle-là.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une toile claque au-dessus des prunes. J'entends la toile, maman ! Tu l'entends, au-dessus ? Oui, elle claque. Ça sent le sucré, un peu chaud. Tu le sens, Nino ? Oui, papa. Un cageot de bois est ouvert. Des prunes violettes y brillent. Sur la caisse, un &lt;emphasis level="moderate"&gt;éclat de cageot&lt;/emphasis&gt; brille. Il brille, papa ! Tu le vois, sur le bois ? Oui, un petit point. Le filet de coton est prêt. Il gratte un peu. On le remplit, Nino ? Oui, avec une prune. Le pain chaud tape le bras de Nino. Il est tiède. Le papier croustille ? Oui, papa. À côté, des pommes rouges attendent. Elles sont lisses, maman. On verra les pommes après ? Après la prune. Une balance fait tic, tout près. J'entends le tic. C'est la balance ? Oui. En ce moment, Nino veut une prune. Je veux une prune, maintenant ! Une prune violette, maman. Avec Mila, Nino ? Oui, maman. Nino saisit trop vite une prune. La prune glisse entre ses doigts. Elle tombe dans le cageot. Elle est tombée ! Nino tire le filet trop vite. Le filet se coince au bord. Il est coincé ! Le coton, Nino ? Il tient au bois. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu, lourdes. Maman s'accroupit à la même hauteur. Tu veux la prune avec Mila ? Oui, maman. Tes mains sont collantes, Nino ? Un peu, papa. Mila arrive près du cageot. Mila ! Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Tu vois Mila, Nino ? Oui, papa. Elles brillent un peu. Elle porte un gilet vert. Tu viens, Mila ? Oui. Nino ouvre la bouche. Un petit rire commence. Oh. Nino ferme la bouche. Il regarde la caisse. Il tend une prune. Pour toi. Mila ne dit rien, d'abord. Elle compte les prunes des yeux. Celle-là. L'éclat de cageot tremble, puis tient.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au marché avec maman. Inès arrive avec des lunettes neuves. Elles brillent un peu. Un camarade ouvre la bouche. Maya ne rit &lt;emphasis&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire de l'apparence. Maman dit : on joue. On ne rit pas des lunettes, des cheveux ou d'un habit. Maya tend une prune à Inès. Elles marchent ensemble. Maya dit : tes lunettes sont là. C'est tout. Pas rire de l'apparence. [pause]</t>
+          <t>Une toile claque au-dessus des prunes. J'entends la toile, maman ! Tu l'entends, au-dessus ? Oui, elle claque. Ça sent le sucré, un peu chaud. Tu le sens, Nino ? Oui, papa. Un cageot de bois est ouvert. Des prunes violettes y brillent. Sur la caisse, un &lt;emphasis&gt;éclat de cageot&lt;/emphasis&gt; brille. Il brille, papa ! Tu le vois, sur le bois ? Oui, un petit point. Le filet de coton est prêt. Il gratte un peu. On le remplit, Nino ? Oui, avec une prune. Le pain chaud tape le bras de Nino. Il est tiède. Le papier croustille ? Oui, papa. À côté, des pommes rouges attendent. Elles sont lisses, maman. On verra les pommes après ? Après la prune. Une balance fait tic, tout près. J'entends le tic. C'est la balance ? Oui. En ce moment, Nino veut une prune. Je veux une prune, maintenant ! Une prune violette, maman. Avec Mila, Nino ? Oui, maman. Nino saisit trop vite une prune. La prune glisse entre ses doigts. Elle tombe dans le cageot. Elle est tombée ! Nino tire le filet trop vite. Le filet se coince au bord. Il est coincé ! Le coton, Nino ? Il tient au bois. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu, lourdes. Maman s'accroupit à la même hauteur. Tu veux la prune avec Mila ? Oui, maman. Tes mains sont collantes, Nino ? Un peu, papa. Mila arrive près du cageot. Mila ! Ses chaussures collent un peu au sol. Mila a des lunettes neuves. Tu vois Mila, Nino ? Oui, papa. Elles brillent un peu. Elle porte un gilet vert. Tu viens, Mila ? Oui. Nino ouvre la bouche. Un petit rire commence. Oh. Nino ferme la bouche. Il regarde la caisse. Il tend une prune. Pour toi. Mila ne dit rien, d'abord. Elle compte les prunes des yeux. Celle-là. L'éclat de cageot tremble, puis tient. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>éclat de cageot</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,46 +1321,85 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_prune_violette_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le four du boulanger souffle une odeur de mie.
-narrateur|Un peu de farine blanchit la planche.
-narrateur|Le pain chaud croustille dans le sac.
-narrateur|Une miette tombe près de la caisse.
-narrateur|Maman tient un filet de coton.
-narrateur|Le filet sent encore la lessive.
-narrateur|Le sol est un peu collant.
-maman|Tu as senti le pain, Nino ?
-enfant-m|Il est chaud.
-maman|Oui.
-maman|Il ira avec la tarte.
-narrateur|Nino touche le sac de pain.
-narrateur|Le papier est tiède.
-narrateur|En ce moment, Nino regarde les prunes.
-narrateur|Elles sont violettes et lisses.
-narrateur|Une caisse sent le sucré.
-enfant-m|J'en veux une ronde.
-enfant-m|Pour la tarte.
-maman|On en cherche une ferme.
-maman|Pas trop molle.
-narrateur|Mila arrive près de la caisse.
+          <t>narrateur|Une toile claque au-dessus des prunes.
+enfant-m|J'entends la toile, maman !
+maman|Tu l'entends, au-dessus ?
+enfant-m|Oui, elle claque.
+narrateur|Ça sent le sucré, un peu chaud.
+papa|Tu le sens, Nino ?
+enfant-m|Oui, papa.
+narrateur|Un cageot de bois est ouvert.
+narrateur|Des prunes violettes y brillent.
+narrateur|Sur la caisse, un éclat de cageot brille.
+enfant-m|Il brille, papa !
+papa|Tu le vois, sur le bois ?
+enfant-m|Oui, un petit point.
+maman|Le filet de coton est prêt.
+enfant-m|Il gratte un peu.
+maman|On le remplit, Nino ?
+enfant-m|Oui, avec une prune.
+narrateur|Le pain chaud tape le bras de Nino.
+enfant-m|Il est tiède.
+papa|Le papier croustille ?
+enfant-m|Oui, papa.
+narrateur|À côté, des pommes rouges attendent.
+enfant-m|Elles sont lisses, maman.
+maman|On verra les pommes après ?
+enfant-m|Après la prune.
+narrateur|Une balance fait tic, tout près.
+enfant-m|J'entends le tic.
+papa|C'est la balance ?
+enfant-m|Oui.
+narrateur|En ce moment, Nino veut une prune.
+enfant-m|Je veux une prune, maintenant !
+enfant-m|Une prune violette, maman.
+maman|Avec Mila, Nino ?
+enfant-m|Oui, maman.
+narrateur|Nino saisit trop vite une prune.
+narrateur|La prune glisse entre ses doigts.
+narrateur|Elle tombe dans le cageot.
+enfant-m|Elle est tombée !
+narrateur|Nino tire le filet trop vite.
+narrateur|Le filet se coince au bord.
+enfant-m|Il est coincé !
+papa|Le coton, Nino ?
+enfant-m|Il tient au bois.
+narrateur|Le sourire de Nino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu, lourdes.
+narrateur|Maman s'accroupit à la même hauteur.
+maman|Tu veux la prune avec Mila ?
+enfant-m|Oui, maman.
+papa|Tes mains sont collantes, Nino ?
+enfant-m|Un peu, papa.
+narrateur|Mila arrive près du cageot.
+enfant-m|Mila !
 narrateur|Ses chaussures collent un peu au sol.
 narrateur|Mila a des lunettes neuves.
-narrateur|Mila a les cheveux lisses.
+papa|Tu vois Mila, Nino ?
+enfant-m|Oui, papa.
+narrateur|Elles brillent un peu.
 narrateur|Elle porte un gilet vert.
-maman|Mila, tu cherches avec Nino.
-enfant-m|Tu m'aides, Mila ?
+enfant-m|Tu viens, Mila ?
 copine|Oui.
-narrateur|Nino prend une prune.
-narrateur|Elle cède un peu sous le doigt.
-enfant-m|Elle est molle.
-maman|On la repose.
-maman|Tout doux, dans la caisse.
-narrateur|Mila se penche sur la caisse.
-narrateur|Elle regarde au fond.
-copine|Au fond.
-copine|Celle-là.</t>
+narrateur|Nino ouvre la bouche.
+narrateur|Un petit rire commence.
+enfant-m|Oh.
+narrateur|Nino ferme la bouche.
+narrateur|Il regarde la caisse.
+narrateur|Il tend une prune.
+enfant-m|Pour toi.
+narrateur|Mila ne dit rien, d'abord.
+narrateur|Elle compte les prunes des yeux.
+copine|Celle-là.
+narrateur|L'éclat de cageot tremble, puis tient.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1397,22 +1436,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila a des lunettes. Que fait Nino ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila a des &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;. Que fait Nino ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Inès a des lunettes. Que fait Maya ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila a des &lt;emphasis&gt;lunettes&lt;/emphasis&gt;. Que fait Nino ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>jouer</t>
+          <t>pas rire</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer | ensemble | aider | prune | on joue | pas rire</t>
+          <t>pas rire | jouer | ensemble</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1427,7 +1466,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Nino écoute Mila. Que fait-il ?</t>
+          <t>On ne rit pas de l'apparence. Que fait Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1465,7 +1504,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1476,7 +1515,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1491,34 +1530,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>lunettes</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1533,17 +1576,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=il_ferme_la_bouche_tend_la_prune; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1576,17 +1619,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Mila a vu au fond. On a la prune. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
+          <t>Nino veut une prune plus brillante. Celle-là brille plus ! Il avance trop vite vers la caisse. Les mots se bousculent dans sa bouche. Non. Mila recule d'un pas. Oh. Le sourire ne revient pas. Nino refuse de foncer. Il referme la main. Personne ne parle. Il observe le cageot, un instant. Nino regarde l'éclat de cageot. Tu veux la prune avec Mila ? Tu prends celle du fond ? Mila ne dit rien, d'abord. Elle pose le doigt sur une prune. Elle est ferme. D'accord. Nino la pose dans le filet. Le coton se tend un peu. Merci, Nino. Maman a vu la prune tendue. Mila, tu as vu le filet ? Oui. On prend une pomme aussi ? Une pomme rouge, Nino ? Oui, maman. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse. Le filet s'alourdit ? Un peu, papa. Tes mains sont propres, Nino ? Un peu collantes. Le ventre de Nino se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino écoute Mila. Il prend la prune du fond. Elle est lisse et ferme. Merci, Nino. Merci, Mila. Elle est ronde. Pour la tarte. On la met dans le filet. Le filet s'alourdit un peu. Le coton se tend. Mila a vu au fond. On a la prune. On prend une pomme aussi ? Oui. Une pomme rouge. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino veut une prune plus brillante. Celle-là brille plus ! Il avance trop vite vers la caisse. Les mots se bousculent dans sa bouche. Non. Mila recule d'un pas. Oh. Le sourire ne revient pas. Nino refuse de foncer. Il referme la main. Personne ne parle. Il observe le cageot, un instant. Nino regarde l'éclat de cageot. Tu veux la prune avec Mila ? Tu prends celle du fond ? Mila ne dit rien, d'abord. Elle pose le doigt sur une prune. Elle est ferme. D'accord. Nino la pose dans le &lt;emphasis level="moderate"&gt;filet&lt;/emphasis&gt;. Le coton se tend un peu. Merci, Nino. Maman a vu la prune tendue. Mila, tu as vu le filet ? Oui. On prend une pomme aussi ? Une pomme rouge, Nino ? Oui, maman. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse. Le filet s'alourdit ? Un peu, papa. Tes mains sont propres, Nino ? Un peu collantes. Le ventre de Nino se desserre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Maya n'a &lt;emphasis&gt;pas&lt;/emphasis&gt; ri. Elle a joué avec Inès. Pas rire de l'apparence. [pause]</t>
+          <t>Nino veut une prune plus brillante. Celle-là brille plus ! Il avance trop vite vers la caisse. Les mots se bousculent dans sa bouche. Non. Mila recule d'un pas. Oh. Le sourire ne revient pas. Nino refuse de foncer. Il referme la main. Personne ne parle. Il observe le cageot, un instant. Nino regarde l'éclat de cageot. Tu veux la prune avec Mila ? Tu prends celle du fond ? Mila ne dit rien, d'abord. Elle pose le doigt sur une prune. Elle est ferme. D'accord. Nino la pose dans le &lt;emphasis&gt;filet&lt;/emphasis&gt;. Le coton se tend un peu. Merci, Nino. Maman a vu la prune tendue. Mila, tu as vu le filet ? Oui. On prend une pomme aussi ? Une pomme rouge, Nino ? Oui, maman. Mila montre une pomme brillante. Nino la pose dans le filet. Elle est lisse. Le filet s'alourdit ? Un peu, papa. Tes mains sont propres, Nino ? Un peu collantes. Le ventre de Nino se desserre. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1633,7 +1676,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1641,10 +1684,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1667,30 +1710,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>filet</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1699,10 +1742,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1715,29 +1758,52 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_ils_posent_la_prune; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino écoute Mila.
-narrateur|Il prend la prune du fond.
-narrateur|Elle est lisse et ferme.
+          <t>narrateur|Nino veut une prune plus brillante.
+enfant-m|Celle-là brille plus !
+narrateur|Il avance trop vite vers la caisse.
+narrateur|Les mots se bousculent dans sa bouche.
+copine|Non.
+narrateur|Mila recule d'un pas.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Nino refuse de foncer.
+narrateur|Il referme la main.
+narrateur|Personne ne parle.
+narrateur|Il observe le cageot, un instant.
+narrateur|Nino regarde l'éclat de cageot.
+papa|Tu veux la prune avec Mila ?
+enfant-m|Tu prends celle du fond ?
+narrateur|Mila ne dit rien, d'abord.
+narrateur|Elle pose le doigt sur une prune.
+copine|Elle est ferme.
+enfant-m|D'accord.
+narrateur|Nino la pose dans le filet.
+narrateur|Le coton se tend un peu.
 maman|Merci, Nino.
-maman|Merci, Mila.
-enfant-m|Elle est ronde.
-copine|Pour la tarte.
-maman|On la met dans le filet.
-narrateur|Le filet s'alourdit un peu.
-narrateur|Le coton se tend.
-maman|Mila a vu au fond.
-maman|On a la prune.
+narrateur|Maman a vu la prune tendue.
+papa|Mila, tu as vu le filet ?
+copine|Oui.
 enfant-m|On prend une pomme aussi ?
-maman|Oui.
-maman|Une pomme rouge.
+maman|Une pomme rouge, Nino ?
+enfant-m|Oui, maman.
 narrateur|Mila montre une pomme brillante.
 narrateur|Nino la pose dans le filet.
-enfant-m|Elle est lisse.</t>
+enfant-m|Elle est lisse.
+papa|Le filet s'alourdit ?
+enfant-m|Un peu, papa.
+maman|Tes mains sont propres, Nino ?
+enfant-m|Un peu collantes.
+narrateur|Le ventre de Nino se desserre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>filet,prune</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1830,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La pomme rejoint la prune. Le filet balance. Il est lourd, le filet ? Un peu. On le porte à deux. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. C'est vert. Vert et frais. Ils passent près des œufs. Les boîtes sont beiges. Bravo. Tu as choisi la prune ferme. Le pain chaud tape le bras. Ce soir, la tarte. Oui. Avec ta prune ronde. Et la pomme. Une balance fait tic près d'eux. Les toiles claquent un peu.</t>
+          <t>Nino veut montrer la prune brillante. Je la porte, maintenant ! Il lève le filet trop haut. Attends. Trop vite, d'un coup. Une prune presse contre le coton. Ça tache ! Un peu de jus glisse sur le gilet. Le gilet, Nino ? Il est taché. Les lunettes de Mila bougent. Nino ouvre la bouche. Un petit rire revient, presque. Oh. Nino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite à voix haute. Il observe le filet, un instant. Il écoute le tic de la balance. Sur la caisse, un éclat de cageot luit. L'éclat, papa ? Tu le vois, toi ? Oui, sur le bois. Le filet, Nino ? On le porte à deux. Nino tient une anse. Mila tient l'autre. Je le tiens. Ils marchent, sans se presser. C'est passé. Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>La pomme rejoint la prune. Le filet balance. Il est lourd, le filet ? Un peu. On le porte à deux. Nino tient une anse. Maman tient l'autre. Mila marche tout près. Un stand de menthe sent fort. Ça pique le nez. C'est la menthe. C'est vert. Vert et frais. Ils passent près des œufs. Les boîtes sont beiges. Bravo. Tu as choisi la prune ferme. Le pain chaud tape le bras. Ce soir, la tarte. Oui. Avec ta prune ronde. Et la pomme. Une balance fait tic près d'eux. Les toiles claquent un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nino veut montrer la prune brillante. Je la porte, maintenant ! Il lève le filet trop haut. Attends. Trop vite, d'un coup. Une prune presse contre le coton. Ça tache ! Un peu de jus glisse sur le gilet. Le gilet, Nino ? Il est taché. Les lunettes de Mila bougent. Nino ouvre la bouche. Un petit rire revient, presque. Oh. Nino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite à voix haute. Il observe le filet, un instant. Il écoute le tic de la balance. Sur la caisse, un &lt;emphasis level="moderate"&gt;éclat de cageot&lt;/emphasis&gt; luit. L'éclat, papa ? Tu le vois, toi ? Oui, sur le bois. Le filet, Nino ? On le porte à deux. Nino tient une anse. Mila tient l'autre. Je le tiens. Ils marchent, sans se presser. C'est passé. Oui.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman achète du pain. Maya donne la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>&lt;low-pitch&gt;Nino veut montrer la prune brillante. Je la porte, maintenant ! Il lève le filet trop haut. Attends. Trop vite, d'un coup. Une prune presse contre le coton. Ça tache ! Un peu de jus glisse sur le gilet. Le gilet, Nino ? Il est taché. Les lunettes de Mila bougent. Nino ouvre la bouche. Un petit rire revient, presque. Oh. Nino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite à voix haute. Il observe le filet, un instant. Il écoute le tic de la balance. Sur la caisse, un &lt;emphasis&gt;éclat de cageot&lt;/emphasis&gt; luit. L'éclat, papa ? Tu le vois, toi ? Oui, sur le bois. Le filet, Nino ? On le porte à deux. Nino tient une anse. Mila tient l'autre. Je le tiens. Ils marchent, sans se presser. C'est passé. Oui.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1821,7 +1887,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1829,22 +1895,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1855,30 +1925,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de cageot</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1887,47 +1957,63 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La pomme rejoint la prune.
-narrateur|Le filet balance.
-maman|Il est lourd, le filet ?
-enfant-m|Un peu.
-maman|On le porte à deux.
+          <t>narrateur|Nino veut montrer la prune brillante.
+enfant-m|Je la porte, maintenant !
+narrateur|Il lève le filet trop haut.
+copine|Attends.
+narrateur|Trop vite, d'un coup.
+narrateur|Une prune presse contre le coton.
+enfant-m|Ça tache !
+narrateur|Un peu de jus glisse sur le gilet.
+papa|Le gilet, Nino ?
+enfant-m|Il est taché.
+narrateur|Les lunettes de Mila bougent.
+narrateur|Nino ouvre la bouche.
+narrateur|Un petit rire revient, presque.
+enfant-m|Oh.
+narrateur|Nino refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite à voix haute.
+narrateur|Il observe le filet, un instant.
+narrateur|Il écoute le tic de la balance.
+narrateur|Sur la caisse, un éclat de cageot luit.
+enfant-m|L'éclat, papa ?
+papa|Tu le vois, toi ?
+enfant-m|Oui, sur le bois.
+maman|Le filet, Nino ?
+enfant-m|On le porte à deux.
 narrateur|Nino tient une anse.
-narrateur|Maman tient l'autre.
-narrateur|Mila marche tout près.
-narrateur|Un stand de menthe sent fort.
-enfant-m|Ça pique le nez.
-maman|C'est la menthe.
-copine|C'est vert.
-maman|Vert et frais.
-narrateur|Ils passent près des œufs.
-narrateur|Les boîtes sont beiges.
-maman|Bravo.
-maman|Tu as choisi la prune ferme.
-narrateur|Le pain chaud tape le bras.
-enfant-m|Ce soir, la tarte.
-maman|Oui.
-maman|Avec ta prune ronde.
-copine|Et la pomme.
-narrateur|Une balance fait tic près d'eux.
-narrateur|Les toiles claquent un peu.</t>
+narrateur|Mila tient l'autre.
+copine|Je le tiens.
+narrateur|Ils marchent, sans se presser.
+enfant-m|C'est passé.
+copine|Oui.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>marche,filet</t>
         </is>
       </c>
     </row>
@@ -1954,17 +2040,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche.</t>
+          <t>Un stand de menthe sent fort. Ça pique le nez, maman. C'est la menthe ? Oui, vert et frais. Tu la sens, Nino ? Oui, papa. Ils passent près des œufs. Les boîtes sont beiges. Tu vois les boîtes, Nino ? Oui, papa. Ils s'assoient sur le banc. On est bien, ici. On a la prune, papa. Tu la vois, dans le filet ? Oui, avec Mila. Et la pomme. Nino pose la prune entre eux. Mila pose la main près. Elle est à nous. Elle est là, Nino. Oui, maman. Le pain chaud reste contre le bras. L'éclat est là, papa. Tu le vois sur le bois ? Oui, papa. Les toiles claquent un peu. Un éclat de cageot tient sur le bois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le filet tient la prune et la pomme. Le sac de pain sent le four. On a la prune de la tarte. Oui. Vous avez cherché ensemble. La farine reste sur la planche.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un stand de menthe sent fort. Ça pique le nez, maman. C'est la menthe ? Oui, vert et frais. Tu la sens, Nino ? Oui, papa. Ils passent près des œufs. Les boîtes sont beiges. Tu vois les boîtes, Nino ? Oui, papa. Ils s'assoient sur le banc. On est bien, ici. On a la prune, papa. Tu la vois, dans le filet ? Oui, avec Mila. Et la pomme. Nino pose la prune entre eux. Mila pose la main près. Elle est à nous. Elle est là, Nino. Oui, maman. Le pain chaud reste contre le bras. L'éclat est là, papa. Tu le vois sur le bois ? Oui, papa. Les toiles claquent un peu. Un &lt;emphasis level="moderate"&gt;éclat de cageot&lt;/emphasis&gt; tient sur le bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un stand de menthe sent fort. Ça pique le nez, maman. C'est la menthe ? Oui, vert et frais. Tu la sens, Nino ? Oui, papa. Ils passent près des œufs. Les boîtes sont beiges. Tu vois les boîtes, Nino ? Oui, papa. Ils s'assoient sur le banc. On est bien, ici. On a la prune, papa. Tu la vois, dans le filet ? Oui, avec Mila. Et la pomme. Nino pose la prune entre eux. Mila pose la main près. Elle est à nous. Elle est là, Nino. Oui, maman. Le pain chaud reste contre le bras. L'éclat est là, papa. Tu le vois sur le bois ? Oui, papa. Les toiles claquent un peu. Un &lt;emphasis&gt;éclat de cageot&lt;/emphasis&gt; tient sur le bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,18 +2097,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2117,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2131,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de cageot</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2154,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,29 +2167,59 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_bois; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le filet tient la prune et la pomme.
-narrateur|Le sac de pain sent le four.
-enfant-m|On a la prune de la tarte.
-maman|Oui.
-maman|Vous avez cherché ensemble.
-narrateur|La farine reste sur la planche.</t>
+          <t>narrateur|Un stand de menthe sent fort.
+enfant-m|Ça pique le nez, maman.
+maman|C'est la menthe ?
+enfant-m|Oui, vert et frais.
+papa|Tu la sens, Nino ?
+enfant-m|Oui, papa.
+narrateur|Ils passent près des œufs.
+narrateur|Les boîtes sont beiges.
+papa|Tu vois les boîtes, Nino ?
+enfant-m|Oui, papa.
+narrateur|Ils s'assoient sur le banc.
+maman|On est bien, ici.
+enfant-m|On a la prune, papa.
+papa|Tu la vois, dans le filet ?
+enfant-m|Oui, avec Mila.
+copine|Et la pomme.
+narrateur|Nino pose la prune entre eux.
+narrateur|Mila pose la main près.
+enfant-m|Elle est à nous.
+maman|Elle est là, Nino.
+enfant-m|Oui, maman.
+narrateur|Le pain chaud reste contre le bras.
+enfant-m|L'éclat est là, papa.
+papa|Tu le vois sur le bois ?
+enfant-m|Oui, papa.
+narrateur|Les toiles claquent un peu.
+narrateur|Un éclat de cageot tient sur le bois.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>prune,menthe</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2205,6 +2325,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
